--- a/Deliverables/SM_Bottom Board/_BOM/eSpark BOM_Bottom (20 Boards).xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/eSpark BOM_Bottom (20 Boards).xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="235">
   <si>
     <t>Component list</t>
   </si>
@@ -229,9 +229,6 @@
     <t>ROTARY ENCODER MAGNETIC 4096PPR</t>
   </si>
   <si>
-    <t>WIDE-FULL SCALE RANGE 6-AXIS MEM</t>
-  </si>
-  <si>
     <t>IC BUF NON-INVERT 5.5V SOT23-5</t>
   </si>
   <si>
@@ -304,9 +301,6 @@
     <t>QFN-24</t>
   </si>
   <si>
-    <t>24-QFN (3x3)</t>
-  </si>
-  <si>
     <t>SOT-23-5</t>
   </si>
   <si>
@@ -379,9 +373,6 @@
     <t>AEAT-8800-Q24</t>
   </si>
   <si>
-    <t>ICM-20649</t>
-  </si>
-  <si>
     <t>SN74LV1T34DBVR</t>
   </si>
   <si>
@@ -445,9 +436,6 @@
     <t>Broadcom Avago</t>
   </si>
   <si>
-    <t>TDK InvenSense</t>
-  </si>
-  <si>
     <t>Microchip</t>
   </si>
   <si>
@@ -674,9 +662,6 @@
   </si>
   <si>
     <t>C123083</t>
-  </si>
-  <si>
-    <t>UTSource</t>
   </si>
   <si>
     <t>C100024</t>
@@ -747,11 +732,26 @@
   <si>
     <t>STM32F407VGT6, STM32F407VET6</t>
   </si>
+  <si>
+    <t>LSM6DSLTR</t>
+  </si>
+  <si>
+    <t>C126672</t>
+  </si>
+  <si>
+    <t>Design change done. Part change done due to unavailability</t>
+  </si>
+  <si>
+    <t>LGA-14</t>
+  </si>
+  <si>
+    <t>LGA-14 Attitude Sensor/Gyroscope</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -1491,7 +1491,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1790,25 +1790,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="33.44140625" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.88671875" customWidth="1"/>
-    <col min="14" max="15" width="19.109375" customWidth="1"/>
-    <col min="16" max="18" width="29.44140625" customWidth="1"/>
-    <col min="20" max="20" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="33.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.85546875" customWidth="1"/>
+    <col min="14" max="15" width="19.140625" customWidth="1"/>
+    <col min="16" max="18" width="29.42578125" customWidth="1"/>
+    <col min="20" max="20" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1828,7 +1828,7 @@
       <c r="Q1" s="82"/>
       <c r="R1" s="82"/>
     </row>
-    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -1852,7 +1852,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="43"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -1876,7 +1876,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="83"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -1900,7 +1900,7 @@
       <c r="Q4" s="59"/>
       <c r="R4" s="84"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -1924,7 +1924,7 @@
       <c r="Q5" s="59"/>
       <c r="R5" s="84"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -1944,7 +1944,7 @@
       <c r="Q6" s="59"/>
       <c r="R6" s="84"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -1964,7 +1964,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="84"/>
     </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -1984,13 +1984,13 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="84"/>
     </row>
-    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>10</v>
@@ -1999,53 +1999,53 @@
         <v>40</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I9" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="O9" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="P9" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="K9" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="M9" s="29" t="s">
+      <c r="Q9" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="N9" s="29" t="s">
+      <c r="R9" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="O9" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="P9" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q9" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="R9" s="31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>11</v>
@@ -2054,22 +2054,22 @@
         <v>41</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>40</v>
       </c>
       <c r="O10" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P10" s="37">
         <v>1.9199999999999998E-2</v>
@@ -2093,38 +2093,38 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E11" s="40" t="s">
         <v>42</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K11" s="40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L11" s="73">
         <v>18</v>
@@ -2137,7 +2137,7 @@
         <v>400</v>
       </c>
       <c r="O11" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P11" s="39">
         <v>1.4E-3</v>
@@ -2147,17 +2147,17 @@
         <v>0.55999999999999994</v>
       </c>
       <c r="R11" s="76" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D12" s="37" t="s">
         <v>12</v>
@@ -2166,22 +2166,22 @@
         <v>43</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
@@ -2194,7 +2194,7 @@
         <v>25</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P12" s="37">
         <v>6.1499999999999999E-2</v>
@@ -2205,14 +2205,14 @@
       </c>
       <c r="R12" s="69"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D13" s="39" t="s">
         <v>13</v>
@@ -2221,22 +2221,22 @@
         <v>44</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="L13" s="39">
         <v>2</v>
@@ -2249,7 +2249,7 @@
         <v>50</v>
       </c>
       <c r="O13" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P13" s="39">
         <v>5.0099999999999999E-2</v>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="R13" s="42"/>
     </row>
-    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D14" s="37" t="s">
         <v>14</v>
@@ -2276,22 +2276,22 @@
         <v>45</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L14" s="37">
         <v>2</v>
@@ -2304,7 +2304,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P14" s="37">
         <v>3.3999999999999998E-3</v>
@@ -2315,14 +2315,14 @@
       </c>
       <c r="R14" s="41"/>
     </row>
-    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>15</v>
@@ -2331,22 +2331,22 @@
         <v>46</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L15" s="39">
         <v>2</v>
@@ -2359,7 +2359,7 @@
         <v>50</v>
       </c>
       <c r="O15" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P15" s="39">
         <v>7.3000000000000001E-3</v>
@@ -2370,14 +2370,14 @@
       </c>
       <c r="R15" s="42"/>
     </row>
-    <row r="16" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D16" s="39" t="s">
         <v>16</v>
@@ -2386,22 +2386,22 @@
         <v>42</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K16" s="40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2414,7 +2414,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P16" s="39">
         <v>1.4E-3</v>
@@ -2425,38 +2425,38 @@
       </c>
       <c r="R16" s="42"/>
     </row>
-    <row r="17" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E17" s="38" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J17" s="37" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L17" s="70">
         <v>1</v>
@@ -2469,7 +2469,7 @@
         <v>25</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P17" s="37">
         <v>0.17119999999999999</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="R17" s="69"/>
     </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D18" s="39" t="s">
         <v>17</v>
@@ -2496,22 +2496,22 @@
         <v>48</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K18" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L18" s="39">
         <v>1</v>
@@ -2524,7 +2524,7 @@
         <v>25</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P18" s="39">
         <v>0.1066</v>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="R18" s="42"/>
     </row>
-    <row r="19" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D19" s="37" t="s">
         <v>18</v>
@@ -2551,22 +2551,22 @@
         <v>49</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J19" s="37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L19" s="37">
         <v>4</v>
@@ -2579,7 +2579,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P19" s="37">
         <v>2.9499999999999998E-2</v>
@@ -2590,14 +2590,14 @@
       </c>
       <c r="R19" s="41"/>
     </row>
-    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>19</v>
@@ -2606,22 +2606,22 @@
         <v>50</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G20" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K20" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L20" s="39">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>25</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="P20" s="39">
         <v>2.09</v>
@@ -2645,14 +2645,14 @@
       </c>
       <c r="R20" s="42"/>
     </row>
-    <row r="21" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D21" s="37" t="s">
         <v>20</v>
@@ -2661,22 +2661,22 @@
         <v>51</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L21" s="37">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>25</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P21" s="37">
         <v>9.8500000000000004E-2</v>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="R21" s="41"/>
     </row>
-    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>21</v>
@@ -2716,22 +2716,22 @@
         <v>52</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" s="40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K22" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L22" s="39">
         <v>1</v>
@@ -2744,7 +2744,7 @@
         <v>30</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P22" s="39">
         <v>4.2200000000000001E-2</v>
@@ -2755,14 +2755,14 @@
       </c>
       <c r="R22" s="42"/>
     </row>
-    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D23" s="37" t="s">
         <v>22</v>
@@ -2771,22 +2771,22 @@
         <v>53</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L23" s="37">
         <v>1</v>
@@ -2799,7 +2799,7 @@
         <v>25</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P23" s="37">
         <v>0.30840000000000001</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="R23" s="41"/>
     </row>
-    <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D24" s="39" t="s">
         <v>23</v>
@@ -2826,22 +2826,22 @@
         <v>54</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G24" s="40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K24" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L24" s="39">
         <v>2</v>
@@ -2854,7 +2854,7 @@
         <v>60</v>
       </c>
       <c r="O24" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P24" s="39">
         <v>3.4799999999999998E-2</v>
@@ -2865,14 +2865,14 @@
       </c>
       <c r="R24" s="42"/>
     </row>
-    <row r="25" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D25" s="37" t="s">
         <v>24</v>
@@ -2881,22 +2881,22 @@
         <v>55</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L25" s="37">
         <v>40</v>
@@ -2909,7 +2909,7 @@
         <v>900</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P25" s="37">
         <v>8.9999999999999998E-4</v>
@@ -2920,14 +2920,14 @@
       </c>
       <c r="R25" s="41"/>
     </row>
-    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>25</v>
@@ -2936,22 +2936,22 @@
         <v>56</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K26" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="L26" s="39">
         <v>7</v>
@@ -2964,7 +2964,7 @@
         <v>200</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P26" s="39">
         <v>1.1999999999999999E-3</v>
@@ -2975,14 +2975,14 @@
       </c>
       <c r="R26" s="42"/>
     </row>
-    <row r="27" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>26</v>
@@ -2991,22 +2991,22 @@
         <v>57</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="J27" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L27" s="37">
         <v>1</v>
@@ -3019,7 +3019,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P27" s="37">
         <v>2.0999999999999999E-3</v>
@@ -3030,14 +3030,14 @@
       </c>
       <c r="R27" s="41"/>
     </row>
-    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>27</v>
@@ -3046,22 +3046,22 @@
         <v>58</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G28" s="40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H28" s="39" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K28" s="40" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L28" s="39">
         <v>2</v>
@@ -3074,7 +3074,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P28" s="39">
         <v>1.4E-3</v>
@@ -3085,38 +3085,38 @@
       </c>
       <c r="R28" s="42"/>
     </row>
-    <row r="29" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D29" s="74" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E29" s="38" t="s">
         <v>59</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L29" s="75">
         <v>2</v>
@@ -3129,7 +3129,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P29" s="37">
         <v>1.4E-3</v>
@@ -3139,17 +3139,17 @@
         <v>0.13999999999999999</v>
       </c>
       <c r="R29" s="69" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D30" s="39" t="s">
         <v>28</v>
@@ -3158,22 +3158,22 @@
         <v>60</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G30" s="40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I30" s="39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K30" s="40" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L30" s="39">
         <v>2</v>
@@ -3186,7 +3186,7 @@
         <v>50</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P30" s="39">
         <v>1.01E-2</v>
@@ -3197,37 +3197,37 @@
       </c>
       <c r="R30" s="42"/>
     </row>
-    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <v>22</v>
       </c>
       <c r="C31" s="77" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D31" s="72" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E31" s="78" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F31" s="72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G31" s="78" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H31" s="72" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I31" s="77" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J31" s="77" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="K31" s="78" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L31" s="72">
         <v>2</v>
@@ -3240,7 +3240,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="79" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P31" s="77">
         <v>1E-3</v>
@@ -3250,17 +3250,17 @@
         <v>0.1</v>
       </c>
       <c r="R31" s="81" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
       <c r="C32" s="62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D32" s="62" t="s">
         <v>29</v>
@@ -3269,22 +3269,22 @@
         <v>61</v>
       </c>
       <c r="F32" s="62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G32" s="63" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H32" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I32" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J32" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K32" s="63" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L32" s="62">
         <v>8</v>
@@ -3297,7 +3297,7 @@
         <v>160</v>
       </c>
       <c r="O32" s="62" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="P32" s="62">
         <v>0</v>
@@ -3307,17 +3307,17 @@
         <v>0</v>
       </c>
       <c r="R32" s="64" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D33" s="39" t="s">
         <v>30</v>
@@ -3326,22 +3326,22 @@
         <v>62</v>
       </c>
       <c r="F33" s="39" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G33" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H33" s="39" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I33" s="39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J33" s="39" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K33" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L33" s="39">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>30</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P33" s="39">
         <v>4.9599999999999998E-2</v>
@@ -3365,14 +3365,14 @@
       </c>
       <c r="R33" s="71"/>
     </row>
-    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D34" s="37" t="s">
         <v>31</v>
@@ -3381,22 +3381,22 @@
         <v>63</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L34" s="37">
         <v>1</v>
@@ -3409,7 +3409,7 @@
         <v>22</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P34" s="37">
         <v>10.947699999999999</v>
@@ -3419,17 +3419,17 @@
         <v>240.84939999999997</v>
       </c>
       <c r="R34" s="69" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D35" s="39" t="s">
         <v>32</v>
@@ -3438,22 +3438,22 @@
         <v>64</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G35" s="40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I35" s="39" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J35" s="39" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K35" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L35" s="39">
         <v>1</v>
@@ -3466,7 +3466,7 @@
         <v>22</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P35" s="39">
         <v>3.0078999999999998</v>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="R35" s="71"/>
     </row>
-    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D36" s="37" t="s">
         <v>33</v>
@@ -3493,22 +3493,22 @@
         <v>65</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -3521,7 +3521,7 @@
         <v>22</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P36" s="37">
         <v>4.2937000000000003</v>
@@ -3532,38 +3532,38 @@
       </c>
       <c r="R36" s="69"/>
     </row>
-    <row r="37" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D37" s="39" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>66</v>
+        <v>234</v>
       </c>
       <c r="F37" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="G37" s="40" t="s">
-        <v>116</v>
+        <v>233</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>230</v>
       </c>
       <c r="H37" s="39" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I37" s="39" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="J37" s="39" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="K37" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L37" s="39">
         <v>1</v>
@@ -3576,49 +3576,51 @@
         <v>22</v>
       </c>
       <c r="O37" s="61" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="P37" s="39">
-        <v>10.6416</v>
+        <v>1.9530000000000001</v>
       </c>
       <c r="Q37" s="42">
         <f t="shared" si="1"/>
-        <v>234.11520000000002</v>
-      </c>
-      <c r="R37" s="42"/>
-    </row>
-    <row r="38" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42.966000000000001</v>
+      </c>
+      <c r="R37" s="76" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D38" s="37" t="s">
         <v>35</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L38" s="37">
         <v>1</v>
@@ -3631,7 +3633,7 @@
         <v>22</v>
       </c>
       <c r="O38" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P38" s="37">
         <v>0.3337</v>
@@ -3642,38 +3644,38 @@
       </c>
       <c r="R38" s="41"/>
     </row>
-    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D39" s="39" t="s">
         <v>36</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F39" s="39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G39" s="40" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I39" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J39" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K39" s="40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L39" s="39">
         <v>1</v>
@@ -3686,7 +3688,7 @@
         <v>22</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P39" s="39">
         <v>1.06</v>
@@ -3697,38 +3699,38 @@
       </c>
       <c r="R39" s="42"/>
     </row>
-    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -3741,7 +3743,7 @@
         <v>22</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P40" s="37">
         <v>0.77</v>
@@ -3752,38 +3754,38 @@
       </c>
       <c r="R40" s="41"/>
     </row>
-    <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D41" s="39" t="s">
         <v>38</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="39" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H41" s="39" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I41" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J41" s="39" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K41" s="40" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L41" s="39">
         <v>1</v>
@@ -3796,7 +3798,7 @@
         <v>22</v>
       </c>
       <c r="O41" s="61" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P41" s="39">
         <v>0.499</v>
@@ -3807,38 +3809,38 @@
       </c>
       <c r="R41" s="42"/>
     </row>
-    <row r="42" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D42" s="37" t="s">
         <v>39</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J42" s="58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="L42" s="37">
         <v>1</v>
@@ -3851,7 +3853,7 @@
         <v>22</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="P42" s="37">
         <v>0.69</v>
@@ -3862,7 +3864,7 @@
       </c>
       <c r="R42" s="41"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="32"/>
       <c r="C43" s="51"/>
@@ -3880,16 +3882,16 @@
       <c r="M43" s="36"/>
       <c r="N43" s="36"/>
       <c r="O43" s="65" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="P43" s="66"/>
       <c r="Q43" s="65">
         <f>SUM(Q10:Q42)</f>
-        <v>794.87919999999997</v>
+        <v>603.73</v>
       </c>
       <c r="R43" s="44"/>
     </row>
-    <row r="44" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="24"/>
       <c r="C44" s="52"/>
@@ -3907,12 +3909,12 @@
       <c r="M44" s="9"/>
       <c r="N44" s="9"/>
       <c r="O44" s="67" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="P44" s="68"/>
       <c r="Q44" s="67">
         <f>Q43/20</f>
-        <v>39.743960000000001</v>
+        <v>30.186500000000002</v>
       </c>
       <c r="R44" s="45"/>
     </row>
